--- a/research/files/bc_transit_stops.xlsx
+++ b/research/files/bc_transit_stops.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Published 2026-07-26 by BC Cycle Tourism Society.</t>
+          <t>Published 2026-08-11 by BC Cycle Tourism Society.</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit stops, in order, with locations [data set]. Version 2026-07-26. https://bccycletourism.ca/research/</t>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit stops, in order, with locations [data set]. Version 2026-08-11. https://bccycletourism.ca/research/</t>
         </is>
       </c>
     </row>

--- a/research/files/bc_transit_stops.xlsx
+++ b/research/files/bc_transit_stops.xlsx
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>49.1661</v>
+        <v>49.16628</v>
       </c>
       <c r="G17" t="n">
-        <v>-123.9307</v>
+        <v>-123.930224</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>49.1661</v>
+        <v>49.16628</v>
       </c>
       <c r="G35" t="n">
-        <v>-123.9307</v>
+        <v>-123.930224</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>49.1661</v>
+        <v>49.16628</v>
       </c>
       <c r="G39" t="n">
-        <v>-123.9307</v>
+        <v>-123.930224</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>49.1661</v>
+        <v>49.16628</v>
       </c>
       <c r="G49" t="n">
-        <v>-123.9307</v>
+        <v>-123.930224</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -18802,10 +18802,10 @@
         </is>
       </c>
       <c r="F450" t="n">
-        <v>49.1661</v>
+        <v>49.16628</v>
       </c>
       <c r="G450" t="n">
-        <v>-123.9307</v>
+        <v>-123.930224</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>49.1778</v>
+        <v>49.178159</v>
       </c>
       <c r="G451" t="n">
         <v>-123.8584</v>

--- a/research/files/bc_transit_stops.xlsx
+++ b/research/files/bc_transit_stops.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Published 2026-08-11 by BC Cycle Tourism Society.</t>
+          <t>Published 2026-09-02 by BC Cycle Tourism Society.</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit stops, in order, with locations [data set]. Version 2026-08-11. https://bccycletourism.ca/research/</t>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit stops, in order, with locations [data set]. Version 2026-09-02. https://bccycletourism.ca/research/</t>
         </is>
       </c>
     </row>
